--- a/Material de apoio/Dados Funcionarios.xlsx
+++ b/Material de apoio/Dados Funcionarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palve\OneDrive\Documentos\GitHub\PowerBi\Material de apoio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{838C8CEB-8F07-49E4-A663-D30FC0C8766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C678551A-15ED-4340-A553-50A120759F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$I$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$M$87</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="124">
   <si>
     <t>Chapa</t>
   </si>
@@ -55,9 +55,6 @@
     <t>ITAMAR MENDES DA SILVEIRA</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>ADALBERTO DE JESUS LIMA</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
     <t>ALESSANDRA LOPES DE ABREU</t>
   </si>
   <si>
@@ -308,6 +302,99 @@
   </si>
   <si>
     <t>ANA FLAVIA CORREA</t>
+  </si>
+  <si>
+    <t>Bairro</t>
+  </si>
+  <si>
+    <t>Cidade</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>Curitiba</t>
+  </si>
+  <si>
+    <t>Paraná</t>
+  </si>
+  <si>
+    <t>São Pedro</t>
+  </si>
+  <si>
+    <t>Campinas</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Cabo Frio</t>
+  </si>
+  <si>
+    <t>Vila américa</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>Maria Fátima</t>
+  </si>
+  <si>
+    <t>Salvador</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Dom Cesar</t>
+  </si>
+  <si>
+    <t>Guarapari</t>
+  </si>
+  <si>
+    <t>Espirito Santo</t>
+  </si>
+  <si>
+    <t>Olimpia</t>
+  </si>
+  <si>
+    <t>Macaé</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>Assistente</t>
+  </si>
+  <si>
+    <t>Analista JR</t>
+  </si>
+  <si>
+    <t>Analista Pleno</t>
+  </si>
+  <si>
+    <t>Analista Senior</t>
+  </si>
+  <si>
+    <t>Consultor</t>
+  </si>
+  <si>
+    <t>Gerente</t>
+  </si>
+  <si>
+    <t>Diretor</t>
+  </si>
+  <si>
+    <t>Estagiário</t>
+  </si>
+  <si>
+    <t>Admissão</t>
+  </si>
+  <si>
+    <t>Demissão</t>
   </si>
 </sst>
 </file>
@@ -702,20 +789,25 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="7" customWidth="1"/>
-    <col min="4" max="5" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5703125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,215 +829,311 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D2" s="4">
-        <v>32933</v>
-      </c>
-      <c r="E2" s="5"/>
+        <v>33025</v>
+      </c>
+      <c r="E2" s="4">
+        <v>36988</v>
+      </c>
       <c r="F2" s="6">
         <v>31</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="9">
-        <v>6238.35</v>
-      </c>
-      <c r="I2" s="4">
-        <v>22138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="9">
+        <v>580</v>
+      </c>
+      <c r="J2" s="4">
+        <v>22110</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D3" s="4">
-        <v>33240</v>
+        <v>32933</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="9">
-        <v>2363.02</v>
-      </c>
-      <c r="I3" s="4">
-        <v>18411</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3" s="9">
+        <v>1501.4</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20495</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D4" s="4">
-        <v>33465</v>
+        <v>33025</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="9">
-        <v>9164.0300000000007</v>
-      </c>
-      <c r="I4" s="4">
-        <v>23067</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="9">
+        <v>2348.83</v>
+      </c>
+      <c r="J4" s="4">
+        <v>24178</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D5" s="4">
-        <v>33025</v>
-      </c>
-      <c r="E5" s="4">
-        <v>36988</v>
-      </c>
+        <v>32933</v>
+      </c>
+      <c r="E5" s="5"/>
       <c r="F5" s="6">
         <v>31</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="9">
-        <v>580</v>
-      </c>
-      <c r="I5" s="4">
-        <v>22110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="9">
+        <v>6238.35</v>
+      </c>
+      <c r="J5" s="4">
+        <v>22138</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D6" s="4">
-        <v>33765</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>33240</v>
+      </c>
+      <c r="E6" s="4">
+        <v>34043</v>
+      </c>
       <c r="F6" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="9">
-        <v>3244.89</v>
-      </c>
-      <c r="I6" s="4">
-        <v>27942</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="9">
+        <v>497</v>
+      </c>
+      <c r="J6" s="4">
+        <v>22429</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D7" s="4">
-        <v>32933</v>
+        <v>33240</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="9">
-        <v>1501.4</v>
-      </c>
-      <c r="I7" s="4">
-        <v>20495</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I7" s="9">
+        <v>2363.02</v>
+      </c>
+      <c r="J7" s="4">
+        <v>18411</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D8" s="4">
-        <v>33240</v>
-      </c>
-      <c r="E8" s="4">
-        <v>34043</v>
-      </c>
+        <v>33465</v>
+      </c>
+      <c r="E8" s="5"/>
       <c r="F8" s="6">
         <v>30</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="9">
-        <v>497</v>
-      </c>
-      <c r="I8" s="4">
-        <v>22429</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I8" s="9">
+        <v>9164.0300000000007</v>
+      </c>
+      <c r="J8" s="4">
+        <v>23067</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D9" s="4">
         <v>33465</v>
@@ -955,51 +1143,75 @@
         <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="9">
+        <v>13</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I9" s="9">
         <v>11815.09</v>
       </c>
-      <c r="I9" s="4">
+      <c r="J9" s="4">
         <v>23432</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D10" s="4">
-        <v>33025</v>
+        <v>33765</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="9">
-        <v>2348.83</v>
-      </c>
-      <c r="I10" s="4">
-        <v>24178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" s="9">
+        <v>3244.89</v>
+      </c>
+      <c r="J10" s="4">
+        <v>27942</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D11" s="4">
         <v>33608</v>
@@ -1009,24 +1221,36 @@
         <v>29</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="9">
+        <v>10</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I11" s="9">
         <v>9764.57</v>
       </c>
-      <c r="I11" s="4">
+      <c r="J11" s="4">
         <v>24217</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="D12" s="4">
         <v>34029</v>
@@ -1038,80 +1262,116 @@
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="9">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="9">
         <v>6080.5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="J12" s="4">
         <v>25429</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D13" s="4">
-        <v>34495</v>
-      </c>
-      <c r="E13" s="5"/>
+        <v>34498</v>
+      </c>
+      <c r="E13" s="4">
+        <v>38485</v>
+      </c>
       <c r="F13" s="6">
         <v>27</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="9">
-        <v>5502.23</v>
-      </c>
-      <c r="I13" s="4">
-        <v>26807</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="9">
+        <v>751.47</v>
+      </c>
+      <c r="J13" s="4">
+        <v>24838</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D14" s="4">
-        <v>34498</v>
-      </c>
-      <c r="E14" s="4">
-        <v>38485</v>
-      </c>
+        <v>34495</v>
+      </c>
+      <c r="E14" s="5"/>
       <c r="F14" s="6">
         <v>27</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="9">
-        <v>751.47</v>
-      </c>
-      <c r="I14" s="4">
-        <v>24838</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="9">
+        <v>5502.23</v>
+      </c>
+      <c r="J14" s="4">
+        <v>26807</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D15" s="4">
         <v>36131</v>
@@ -1121,132 +1381,194 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="9">
+        <v>10</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" s="9">
         <v>2348.83</v>
       </c>
-      <c r="I15" s="4">
+      <c r="J15" s="4">
         <v>20224</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D16" s="4">
-        <v>36052</v>
+        <v>36085</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="6">
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="9">
-        <v>4636.2299999999996</v>
-      </c>
-      <c r="I16" s="4">
-        <v>23888</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I16" s="9">
+        <v>4240.6099999999997</v>
+      </c>
+      <c r="J16" s="4">
+        <v>25204</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D17" s="4">
-        <v>36647</v>
+        <v>36052</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="9">
-        <v>3308.25</v>
-      </c>
-      <c r="I17" s="4">
-        <v>25437</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="9">
+        <v>4636.2299999999996</v>
+      </c>
+      <c r="J17" s="4">
+        <v>23888</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D18" s="4">
-        <v>36647</v>
+        <v>36085</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="9">
-        <v>3308.25</v>
-      </c>
-      <c r="I18" s="4">
-        <v>26587</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="9">
+        <v>4861.6499999999996</v>
+      </c>
+      <c r="J18" s="4">
+        <v>25541</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D19" s="4">
         <v>36647</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="4">
+        <v>38483</v>
+      </c>
       <c r="F19" s="6">
         <v>21</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="9">
-        <v>3780.81</v>
-      </c>
-      <c r="I19" s="4">
-        <v>26678</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="9">
+        <v>1120</v>
+      </c>
+      <c r="J19" s="4">
+        <v>22150</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D20" s="4">
         <v>36647</v>
@@ -1256,51 +1578,77 @@
         <v>21</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="9">
-        <v>2599.31</v>
-      </c>
-      <c r="I20" s="4">
-        <v>23795</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="9">
+        <v>1417.8</v>
+      </c>
+      <c r="J20" s="4">
+        <v>22172</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D21" s="4">
-        <v>36647</v>
-      </c>
-      <c r="E21" s="5"/>
+        <v>36540</v>
+      </c>
+      <c r="E21" s="4">
+        <v>42342</v>
+      </c>
       <c r="F21" s="6">
         <v>21</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="9">
-        <v>3308.25</v>
-      </c>
-      <c r="I21" s="4">
-        <v>26938</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" s="9">
+        <v>2287.79</v>
+      </c>
+      <c r="J21" s="4">
+        <v>25835</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D22" s="4">
         <v>36647</v>
@@ -1310,51 +1658,75 @@
         <v>21</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="9">
-        <v>4017.12</v>
-      </c>
-      <c r="I22" s="4">
-        <v>23012</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="9">
+        <v>2599.31</v>
+      </c>
+      <c r="J22" s="4">
+        <v>23795</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D23" s="4">
-        <v>36647</v>
+        <v>36528</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="6">
         <v>21</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="9">
-        <v>3402.75</v>
-      </c>
-      <c r="I23" s="4">
-        <v>29877</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="9">
+        <v>2650.85</v>
+      </c>
+      <c r="J23" s="4">
+        <v>25673</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D24" s="4">
         <v>36647</v>
@@ -1364,24 +1736,36 @@
         <v>21</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="9">
-        <v>1417.8</v>
-      </c>
-      <c r="I24" s="4">
-        <v>22172</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="9">
+        <v>3308.25</v>
+      </c>
+      <c r="J24" s="4">
+        <v>25437</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D25" s="4">
         <v>36647</v>
@@ -1391,24 +1775,36 @@
         <v>21</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="9">
+        <v>10</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" s="9">
         <v>3308.25</v>
       </c>
-      <c r="I25" s="4">
-        <v>27818</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="4">
+        <v>26587</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D26" s="4">
         <v>36647</v>
@@ -1418,24 +1814,36 @@
         <v>21</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="9">
-        <v>4017.12</v>
-      </c>
-      <c r="I26" s="4">
-        <v>25829</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I26" s="9">
+        <v>3308.25</v>
+      </c>
+      <c r="J26" s="4">
+        <v>26938</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D27" s="4">
         <v>36647</v>
@@ -1445,24 +1853,36 @@
         <v>21</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="9">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="9">
         <v>3308.25</v>
       </c>
-      <c r="I27" s="4">
-        <v>29207</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="4">
+        <v>27818</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D28" s="4">
         <v>36647</v>
@@ -1472,24 +1892,36 @@
         <v>21</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="9">
+        <v>10</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" s="9">
         <v>3308.25</v>
       </c>
-      <c r="I28" s="4">
-        <v>24333</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="4">
+        <v>29207</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D29" s="4">
         <v>36647</v>
@@ -1499,24 +1931,36 @@
         <v>21</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="9">
-        <v>7089.05</v>
-      </c>
-      <c r="I29" s="4">
-        <v>23111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I29" s="9">
+        <v>3308.25</v>
+      </c>
+      <c r="J29" s="4">
+        <v>24333</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D30" s="4">
         <v>36647</v>
@@ -1526,217 +1970,313 @@
         <v>21</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="9">
+        <v>10</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I30" s="9">
         <v>3308.25</v>
       </c>
-      <c r="I30" s="4">
+      <c r="J30" s="4">
         <v>21916</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D31" s="4">
         <v>36647</v>
       </c>
-      <c r="E31" s="4">
-        <v>38483</v>
-      </c>
+      <c r="E31" s="5"/>
       <c r="F31" s="6">
         <v>21</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="9">
-        <v>1120</v>
-      </c>
-      <c r="I31" s="4">
-        <v>22150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I31" s="9">
+        <v>3402.75</v>
+      </c>
+      <c r="J31" s="4">
+        <v>29877</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D32" s="4">
-        <v>36982</v>
+        <v>36647</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="9">
-        <v>2339.39</v>
-      </c>
-      <c r="I32" s="4">
-        <v>24061</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I32" s="9">
+        <v>3780.81</v>
+      </c>
+      <c r="J32" s="4">
+        <v>26678</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D33" s="4">
-        <v>36982</v>
+        <v>36647</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="9">
-        <v>2718.28</v>
-      </c>
-      <c r="I33" s="4">
-        <v>20782</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I33" s="9">
+        <v>4017.12</v>
+      </c>
+      <c r="J33" s="4">
+        <v>23012</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D34" s="4">
-        <v>36982</v>
+        <v>36647</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="9">
-        <v>3031.49</v>
-      </c>
-      <c r="I34" s="4">
-        <v>25665</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" s="9">
+        <v>4017.12</v>
+      </c>
+      <c r="J34" s="4">
+        <v>25829</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D35" s="4">
-        <v>36982</v>
+        <v>36647</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="9">
-        <v>2700.15</v>
-      </c>
-      <c r="I35" s="4">
-        <v>23927</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I35" s="9">
+        <v>7089.05</v>
+      </c>
+      <c r="J35" s="4">
+        <v>23111</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D36" s="4">
         <v>36982</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="4">
+        <v>38474</v>
+      </c>
       <c r="F36" s="6">
         <v>20</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="9">
-        <v>2653.99</v>
-      </c>
-      <c r="I36" s="4">
-        <v>21302</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I36" s="9">
+        <v>792</v>
+      </c>
+      <c r="J36" s="4">
+        <v>32905</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="D37" s="4">
         <v>36982</v>
       </c>
       <c r="E37" s="4">
-        <v>38474</v>
+        <v>40853</v>
       </c>
       <c r="F37" s="6">
         <v>20</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H37" s="9">
-        <v>792</v>
-      </c>
-      <c r="I37" s="4">
-        <v>32905</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I37" s="9">
+        <v>1369.73</v>
+      </c>
+      <c r="J37" s="4">
+        <v>26394</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D38" s="4">
         <v>36982</v>
@@ -1746,53 +2286,75 @@
         <v>20</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="9">
-        <v>2693.85</v>
-      </c>
-      <c r="I38" s="4">
-        <v>25597</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I38" s="9">
+        <v>2339.39</v>
+      </c>
+      <c r="J38" s="4">
+        <v>24061</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D39" s="4">
         <v>36982</v>
       </c>
-      <c r="E39" s="4">
-        <v>40853</v>
-      </c>
+      <c r="E39" s="5"/>
       <c r="F39" s="6">
         <v>20</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="9">
-        <v>1369.73</v>
-      </c>
-      <c r="I39" s="4">
-        <v>26394</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I39" s="9">
+        <v>2653.99</v>
+      </c>
+      <c r="J39" s="4">
+        <v>21302</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D40" s="4">
         <v>36982</v>
@@ -1802,132 +2364,192 @@
         <v>20</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H40" s="9">
-        <v>3308.25</v>
-      </c>
-      <c r="I40" s="4">
-        <v>25866</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I40" s="9">
+        <v>2693.85</v>
+      </c>
+      <c r="J40" s="4">
+        <v>25597</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D41" s="4">
-        <v>38200</v>
+        <v>36982</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H41" s="9">
-        <v>2120</v>
-      </c>
-      <c r="I41" s="4">
-        <v>22358</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I41" s="9">
+        <v>2700.15</v>
+      </c>
+      <c r="J41" s="4">
+        <v>23927</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D42" s="4">
-        <v>38200</v>
+        <v>36982</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H42" s="9">
-        <v>1610</v>
-      </c>
-      <c r="I42" s="4">
-        <v>21742</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I42" s="9">
+        <v>2718.28</v>
+      </c>
+      <c r="J42" s="4">
+        <v>20782</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D43" s="4">
-        <v>38200</v>
+        <v>36982</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="9">
-        <v>1610</v>
-      </c>
-      <c r="I43" s="4">
-        <v>20117</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I43" s="9">
+        <v>3031.49</v>
+      </c>
+      <c r="J43" s="4">
+        <v>25665</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D44" s="4">
-        <v>38200</v>
+        <v>36982</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="9">
-        <v>2820</v>
-      </c>
-      <c r="I44" s="4">
-        <v>24226</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I44" s="9">
+        <v>3308.25</v>
+      </c>
+      <c r="J44" s="4">
+        <v>25866</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D45" s="4">
         <v>38200</v>
@@ -1937,24 +2559,36 @@
         <v>17</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="9">
-        <v>1944.6</v>
-      </c>
-      <c r="I45" s="4">
-        <v>19180</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I45" s="9">
+        <v>1610</v>
+      </c>
+      <c r="J45" s="4">
+        <v>21742</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D46" s="4">
         <v>38200</v>
@@ -1964,545 +2598,785 @@
         <v>17</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="9">
-        <v>2500</v>
-      </c>
-      <c r="I46" s="4">
-        <v>25315</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I46" s="9">
+        <v>1610</v>
+      </c>
+      <c r="J46" s="4">
+        <v>20117</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D47" s="4">
-        <v>36528</v>
+        <v>38200</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="9">
-        <v>2650.85</v>
-      </c>
-      <c r="I47" s="4">
-        <v>25673</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I47" s="9">
+        <v>1944.6</v>
+      </c>
+      <c r="J47" s="4">
+        <v>19180</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D48" s="4">
-        <v>36085</v>
+        <v>38200</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="6">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="9">
-        <v>4861.6499999999996</v>
-      </c>
-      <c r="I48" s="4">
-        <v>25541</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I48" s="9">
+        <v>2120</v>
+      </c>
+      <c r="J48" s="4">
+        <v>22358</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D49" s="4">
-        <v>36085</v>
+        <v>38200</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="6">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="9">
-        <v>4240.6099999999997</v>
-      </c>
-      <c r="I49" s="4">
-        <v>25204</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I49" s="9">
+        <v>2500</v>
+      </c>
+      <c r="J49" s="4">
+        <v>25315</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D50" s="4">
-        <v>40215</v>
+        <v>38200</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" s="9">
-        <v>1557.21</v>
-      </c>
-      <c r="I50" s="4">
-        <v>30168</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I50" s="9">
+        <v>2820</v>
+      </c>
+      <c r="J50" s="4">
+        <v>24226</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D51" s="4">
-        <v>40240</v>
+        <v>40330</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="6">
         <v>11</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" s="9">
-        <v>1465.12</v>
-      </c>
-      <c r="I51" s="4">
-        <v>26395</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I51" s="9">
+        <v>1054.9000000000001</v>
+      </c>
+      <c r="J51" s="4">
+        <v>33332</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D52" s="4">
-        <v>40330</v>
+        <v>40240</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="6">
         <v>11</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H52" s="9">
-        <v>1054.9000000000001</v>
-      </c>
-      <c r="I52" s="4">
-        <v>33332</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I52" s="9">
+        <v>1465.12</v>
+      </c>
+      <c r="J52" s="4">
+        <v>26395</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D53" s="4">
-        <v>40639</v>
+        <v>40215</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" s="9">
-        <v>1265.54</v>
-      </c>
-      <c r="I53" s="4">
-        <v>32602</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I53" s="9">
+        <v>1557.21</v>
+      </c>
+      <c r="J53" s="4">
+        <v>30168</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D54" s="4">
-        <v>40761</v>
-      </c>
-      <c r="E54" s="5"/>
+        <v>40821</v>
+      </c>
+      <c r="E54" s="4">
+        <v>41164</v>
+      </c>
       <c r="F54" s="6">
         <v>10</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" s="9">
-        <v>1111.3499999999999</v>
-      </c>
-      <c r="I54" s="4">
-        <v>34428</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I54" s="9">
+        <v>950</v>
+      </c>
+      <c r="J54" s="4">
+        <v>33334</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D55" s="4">
+        <v>40848</v>
+      </c>
+      <c r="E55" s="4">
+        <v>41164</v>
+      </c>
+      <c r="F55" s="6">
+        <v>10</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I55" s="9">
+        <v>950</v>
+      </c>
+      <c r="J55" s="4">
+        <v>34616</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>53</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="4">
+        <v>40761</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6">
+        <v>10</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I56" s="9">
+        <v>1111.3499999999999</v>
+      </c>
+      <c r="J56" s="4">
+        <v>34428</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="11">
+        <v>52</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D57" s="4">
+        <v>40639</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6">
+        <v>10</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I57" s="9">
+        <v>1265.54</v>
+      </c>
+      <c r="J57" s="4">
+        <v>32602</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>54</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58" s="4">
         <v>40817</v>
-      </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="6">
-        <v>10</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="9">
-        <v>3452.93</v>
-      </c>
-      <c r="I55" s="4">
-        <v>27245</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="11">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" s="4">
-        <v>40821</v>
-      </c>
-      <c r="E56" s="4">
-        <v>41164</v>
-      </c>
-      <c r="F56" s="6">
-        <v>10</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H56" s="9">
-        <v>950</v>
-      </c>
-      <c r="I56" s="4">
-        <v>33334</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="11">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="4">
-        <v>40848</v>
-      </c>
-      <c r="E57" s="4">
-        <v>41164</v>
-      </c>
-      <c r="F57" s="6">
-        <v>10</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="9">
-        <v>950</v>
-      </c>
-      <c r="I57" s="4">
-        <v>34616</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="11">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="4">
-        <v>40826</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="6">
         <v>10</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H58" s="9">
-        <v>4657.4399999999996</v>
-      </c>
-      <c r="I58" s="4">
-        <v>32857</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I58" s="9">
+        <v>3452.93</v>
+      </c>
+      <c r="J58" s="4">
+        <v>27245</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D59" s="4">
-        <v>41036</v>
+        <v>40826</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H59" s="9">
-        <v>1499.51</v>
-      </c>
-      <c r="I59" s="4">
-        <v>24838</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I59" s="9">
+        <v>4657.4399999999996</v>
+      </c>
+      <c r="J59" s="4">
+        <v>32857</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D60" s="4">
-        <v>41169</v>
+        <v>41036</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="6">
         <v>9</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" s="9">
-        <v>3997.28</v>
-      </c>
-      <c r="I60" s="4">
-        <v>25835</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I60" s="9">
+        <v>1499.51</v>
+      </c>
+      <c r="J60" s="4">
+        <v>24838</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D61" s="4">
-        <v>41306</v>
+        <v>41169</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="9">
-        <v>5768.07</v>
-      </c>
-      <c r="I61" s="4">
-        <v>29793</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I61" s="9">
+        <v>3997.28</v>
+      </c>
+      <c r="J61" s="4">
+        <v>25835</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D62" s="4">
         <v>41306</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="4">
+        <v>42035</v>
+      </c>
       <c r="F62" s="6">
         <v>8</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H62" s="9">
-        <v>1366.5</v>
-      </c>
-      <c r="I62" s="4">
-        <v>21961</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I62" s="9">
+        <v>967.5</v>
+      </c>
+      <c r="J62" s="4">
+        <v>34312</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D63" s="4">
         <v>41306</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="4">
+        <v>42035</v>
+      </c>
       <c r="F63" s="6">
         <v>8</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="9">
-        <v>1126.1400000000001</v>
-      </c>
-      <c r="I63" s="4">
-        <v>24030</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I63" s="9">
+        <v>967.5</v>
+      </c>
+      <c r="J63" s="4">
+        <v>34982</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D64" s="4">
         <v>41306</v>
       </c>
-      <c r="E64" s="4">
-        <v>42035</v>
-      </c>
+      <c r="E64" s="5"/>
       <c r="F64" s="6">
         <v>8</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H64" s="9">
-        <v>967.5</v>
-      </c>
-      <c r="I64" s="4">
-        <v>34312</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I64" s="9">
+        <v>1126.1400000000001</v>
+      </c>
+      <c r="J64" s="4">
+        <v>24030</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D65" s="4">
         <v>41306</v>
       </c>
-      <c r="E65" s="4">
-        <v>42035</v>
-      </c>
+      <c r="E65" s="5"/>
       <c r="F65" s="6">
         <v>8</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" s="9">
-        <v>967.5</v>
-      </c>
-      <c r="I65" s="4">
-        <v>34982</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I65" s="9">
+        <v>1359.62</v>
+      </c>
+      <c r="J65" s="4">
+        <v>34677</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D66" s="4">
         <v>41306</v>
@@ -2512,24 +3386,36 @@
         <v>8</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H66" s="9">
-        <v>1359.62</v>
-      </c>
-      <c r="I66" s="4">
-        <v>34677</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I66" s="9">
+        <v>1366.5</v>
+      </c>
+      <c r="J66" s="4">
+        <v>21961</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D67" s="4">
         <v>41306</v>
@@ -2539,24 +3425,36 @@
         <v>8</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" s="9">
+        <v>13</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I67" s="9">
         <v>1689.22</v>
       </c>
-      <c r="I67" s="4">
+      <c r="J67" s="4">
         <v>32344</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K67" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D68" s="4">
         <v>41306</v>
@@ -2566,24 +3464,36 @@
         <v>8</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" s="9">
+        <v>13</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I68" s="9">
         <v>4394.71</v>
       </c>
-      <c r="I68" s="4">
+      <c r="J68" s="4">
         <v>28954</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K68" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D69" s="4">
         <v>41306</v>
@@ -2593,24 +3503,36 @@
         <v>8</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" s="9">
+        <v>13</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I69" s="9">
         <v>4650.22</v>
       </c>
-      <c r="I69" s="4">
+      <c r="J69" s="4">
         <v>31016</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K69" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D70" s="4">
         <v>41306</v>
@@ -2620,51 +3542,75 @@
         <v>8</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H70" s="9">
+        <v>10</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I70" s="9">
         <v>5033.4799999999996</v>
       </c>
-      <c r="I70" s="4">
+      <c r="J70" s="4">
         <v>31009</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K70" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D71" s="4">
-        <v>41730</v>
+        <v>41306</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" s="9">
-        <v>1153.79</v>
-      </c>
-      <c r="I71" s="4">
-        <v>35718</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I71" s="9">
+        <v>5768.07</v>
+      </c>
+      <c r="J71" s="4">
+        <v>29793</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D72" s="4">
         <v>41730</v>
@@ -2674,24 +3620,36 @@
         <v>7</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H72" s="9">
+        <v>13</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I72" s="9">
         <v>1153.79</v>
       </c>
-      <c r="I72" s="4">
-        <v>35064</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J72" s="4">
+        <v>35718</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D73" s="4">
         <v>41730</v>
@@ -2701,78 +3659,114 @@
         <v>7</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H73" s="9">
-        <v>3500</v>
-      </c>
-      <c r="I73" s="4">
-        <v>32727</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I73" s="9">
+        <v>1153.79</v>
+      </c>
+      <c r="J73" s="4">
+        <v>35064</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D74" s="4">
-        <v>41730</v>
+        <v>41913</v>
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="6">
         <v>7</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" s="9">
-        <v>3241.1</v>
-      </c>
-      <c r="I74" s="4">
-        <v>32983</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I74" s="9">
+        <v>1533.04</v>
+      </c>
+      <c r="J74" s="4">
+        <v>30243</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D75" s="4">
-        <v>41730</v>
+        <v>41913</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="6">
         <v>7</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" s="9">
-        <v>21345.119999999999</v>
-      </c>
-      <c r="I75" s="4">
-        <v>22166</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I75" s="9">
+        <v>1533.04</v>
+      </c>
+      <c r="J75" s="4">
+        <v>33155</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D76" s="4">
         <v>41730</v>
@@ -2782,217 +3776,311 @@
         <v>7</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H76" s="9">
-        <v>21345.119999999999</v>
-      </c>
-      <c r="I76" s="4">
-        <v>33238</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I76" s="9">
+        <v>3241.1</v>
+      </c>
+      <c r="J76" s="4">
+        <v>32983</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D77" s="4">
-        <v>41913</v>
+        <v>41730</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="6">
         <v>7</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H77" s="9">
-        <v>1533.04</v>
-      </c>
-      <c r="I77" s="4">
-        <v>30243</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I77" s="9">
+        <v>3500</v>
+      </c>
+      <c r="J77" s="4">
+        <v>32727</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D78" s="4">
-        <v>41913</v>
+        <v>41730</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="6">
         <v>7</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78" s="9">
-        <v>1533.04</v>
-      </c>
-      <c r="I78" s="4">
-        <v>33155</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I78" s="9">
+        <v>21345.119999999999</v>
+      </c>
+      <c r="J78" s="4">
+        <v>22166</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="11">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D79" s="4">
-        <v>36540</v>
-      </c>
-      <c r="E79" s="4">
-        <v>42342</v>
-      </c>
+        <v>41730</v>
+      </c>
+      <c r="E79" s="5"/>
       <c r="F79" s="6">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H79" s="9">
-        <v>2287.79</v>
-      </c>
-      <c r="I79" s="4">
-        <v>25835</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I79" s="9">
+        <v>21345.119999999999</v>
+      </c>
+      <c r="J79" s="4">
+        <v>33238</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D80" s="4">
-        <v>42036</v>
+        <v>42278</v>
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="6">
         <v>6</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H80" s="9">
-        <v>1527.1</v>
-      </c>
-      <c r="I80" s="4">
-        <v>34312</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I80" s="9">
+        <v>1083.83</v>
+      </c>
+      <c r="J80" s="4">
+        <v>33068</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="11">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D81" s="4">
-        <v>42036</v>
-      </c>
-      <c r="E81" s="5"/>
+        <v>42095</v>
+      </c>
+      <c r="E81" s="4">
+        <v>43101</v>
+      </c>
       <c r="F81" s="6">
         <v>6</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="9">
-        <v>1527.1</v>
-      </c>
-      <c r="I81" s="4">
-        <v>34982</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I81" s="9">
+        <v>1210</v>
+      </c>
+      <c r="J81" s="4">
+        <v>32769</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="11">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D82" s="4">
-        <v>42095</v>
-      </c>
-      <c r="E82" s="4">
-        <v>43101</v>
-      </c>
+        <v>42036</v>
+      </c>
+      <c r="E82" s="5"/>
       <c r="F82" s="6">
         <v>6</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H82" s="9">
-        <v>1210</v>
-      </c>
-      <c r="I82" s="4">
-        <v>32769</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I82" s="9">
+        <v>1527.1</v>
+      </c>
+      <c r="J82" s="4">
+        <v>34312</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D83" s="4">
-        <v>42278</v>
+        <v>42036</v>
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="6">
         <v>6</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H83" s="9">
-        <v>1083.83</v>
-      </c>
-      <c r="I83" s="4">
-        <v>33068</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I83" s="9">
+        <v>1527.1</v>
+      </c>
+      <c r="J83" s="4">
+        <v>34982</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="11">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D84" s="4">
         <v>42736</v>
@@ -3002,24 +4090,36 @@
         <v>4</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H84" s="9">
-        <v>2120</v>
-      </c>
-      <c r="I84" s="4">
-        <v>29511</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I84" s="9">
+        <v>405</v>
+      </c>
+      <c r="J84" s="4">
+        <v>32884</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D85" s="4">
         <v>42736</v>
@@ -3029,24 +4129,36 @@
         <v>4</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H85" s="9">
-        <v>405</v>
-      </c>
-      <c r="I85" s="4">
-        <v>32884</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I85" s="9">
+        <v>2120</v>
+      </c>
+      <c r="J85" s="4">
+        <v>29511</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11">
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D86" s="4">
         <v>42737</v>
@@ -3056,24 +4168,36 @@
         <v>4</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H86" s="9">
+        <v>10</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I86" s="9">
         <v>2160.73</v>
       </c>
-      <c r="I86" s="4">
+      <c r="J86" s="4">
         <v>32994</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K86" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="11">
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D87" s="4">
         <v>42745</v>
@@ -3083,19 +4207,31 @@
         <v>4</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="9">
+        <v>13</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I87" s="9">
         <v>4321.47</v>
       </c>
-      <c r="I87" s="4">
+      <c r="J87" s="4">
         <v>28780</v>
       </c>
+      <c r="K87" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I87" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I87">
-      <sortCondition ref="A1:A87"/>
+  <autoFilter ref="A1:M87" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M87">
+      <sortCondition descending="1" ref="F1:F87"/>
     </sortState>
   </autoFilter>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
